--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.01462004343125</v>
+        <v>6.339875757057579</v>
       </c>
       <c r="D2" t="n">
-        <v>38.75977863694505</v>
+        <v>6.298464028503571</v>
       </c>
       <c r="E2" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F2" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.47207040007701</v>
+        <v>4.626711440012515</v>
       </c>
       <c r="D3" t="n">
-        <v>42.6810233369166</v>
+        <v>6.935666292248948</v>
       </c>
       <c r="E3" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F3" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.53391281157681</v>
+        <v>5.449260831881232</v>
       </c>
       <c r="D4" t="n">
-        <v>33.37408619873229</v>
+        <v>5.423289007293997</v>
       </c>
       <c r="E4" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F4" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.08124638462483</v>
+        <v>2.125702537501534</v>
       </c>
       <c r="D5" t="n">
-        <v>27.70116755207308</v>
+        <v>4.501439727211876</v>
       </c>
       <c r="E5" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F5" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.49888709648616</v>
+        <v>2.031069153179001</v>
       </c>
       <c r="D6" t="n">
-        <v>12.73499265911705</v>
+        <v>2.069436307106521</v>
       </c>
       <c r="E6" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F6" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.41443750149546</v>
+        <v>4.292346093993012</v>
       </c>
       <c r="D7" t="n">
-        <v>26.65426879323994</v>
+        <v>4.331318678901491</v>
       </c>
       <c r="E7" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F7" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.08033964158815</v>
+        <v>5.863055191758074</v>
       </c>
       <c r="D8" t="n">
-        <v>36.28679644329956</v>
+        <v>5.896604422036178</v>
       </c>
       <c r="E8" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F8" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.30377456403849</v>
+        <v>2.324363366656255</v>
       </c>
       <c r="D9" t="n">
-        <v>10.67987719890593</v>
+        <v>1.735480044822214</v>
       </c>
       <c r="E9" t="n">
-        <v>10.10795745085423</v>
+        <v>1.642543085763813</v>
       </c>
       <c r="F9" t="n">
-        <v>10.95899995298599</v>
+        <v>1.780837492360223</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
